--- a/pipeline/ArchitectureDesignAndAudit/ProviderSchemaEditsForPipelineAndRuntimeTypeOneTypeTwo_V4.xlsx
+++ b/pipeline/ArchitectureDesignAndAudit/ProviderSchemaEditsForPipelineAndRuntimeTypeOneTypeTwo_V4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CHATHealthyLLC\pipeline\ArchitectureDesignAndAudit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CC9F49F-75B0-4065-BC3C-24E245DAD482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5114F3-B1BB-4EB7-B088-89DCCED6B82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="30915" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -516,7 +516,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -548,8 +548,26 @@
         <fgColor rgb="FF0B7A75"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -557,21 +575,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -884,7 +934,7 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="33.6640625" customWidth="1"/>
+    <col min="6" max="6" width="33.6640625" style="5" customWidth="1"/>
     <col min="7" max="7" width="62" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
@@ -905,187 +955,187 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="b">
+      <c r="F2" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="b">
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="b">
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="A5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="b">
+      <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="B6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F6" t="b">
+      <c r="F6" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="b">
+      <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="A8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="b">
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="A9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="b">
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+      <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="B10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F10" t="b">
+      <c r="F10" s="6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1105,6 +1155,7 @@
       <c r="E11" t="s">
         <v>22</v>
       </c>
+      <c r="F11"/>
     </row>
     <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
@@ -1122,6 +1173,7 @@
       <c r="E12" t="s">
         <v>11</v>
       </c>
+      <c r="F12"/>
     </row>
     <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
@@ -1139,6 +1191,7 @@
       <c r="E13" t="s">
         <v>25</v>
       </c>
+      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
@@ -1156,24 +1209,25 @@
       <c r="E14" t="s">
         <v>11</v>
       </c>
+      <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
+      <c r="A15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="B15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F15" t="b">
+      <c r="F15" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1193,6 +1247,7 @@
       <c r="E16" t="s">
         <v>29</v>
       </c>
+      <c r="F16"/>
     </row>
     <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
@@ -1210,6 +1265,7 @@
       <c r="E17" t="s">
         <v>11</v>
       </c>
+      <c r="F17"/>
     </row>
     <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
@@ -1227,6 +1283,7 @@
       <c r="E18" t="s">
         <v>11</v>
       </c>
+      <c r="F18"/>
     </row>
     <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
@@ -1244,6 +1301,7 @@
       <c r="E19" t="s">
         <v>11</v>
       </c>
+      <c r="F19"/>
     </row>
     <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
@@ -1261,6 +1319,7 @@
       <c r="E20" t="s">
         <v>11</v>
       </c>
+      <c r="F20"/>
     </row>
     <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
@@ -1278,6 +1337,7 @@
       <c r="E21" t="s">
         <v>11</v>
       </c>
+      <c r="F21"/>
     </row>
     <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
@@ -1295,6 +1355,7 @@
       <c r="E22" t="s">
         <v>11</v>
       </c>
+      <c r="F22"/>
     </row>
     <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
@@ -1312,6 +1373,7 @@
       <c r="E23" t="s">
         <v>11</v>
       </c>
+      <c r="F23"/>
     </row>
     <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
@@ -1329,6 +1391,7 @@
       <c r="E24" t="s">
         <v>11</v>
       </c>
+      <c r="F24"/>
     </row>
     <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
@@ -1346,6 +1409,7 @@
       <c r="E25" t="s">
         <v>11</v>
       </c>
+      <c r="F25"/>
     </row>
     <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
@@ -1363,6 +1427,7 @@
       <c r="E26" t="s">
         <v>11</v>
       </c>
+      <c r="F26"/>
     </row>
     <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
@@ -1380,24 +1445,25 @@
       <c r="E27" t="s">
         <v>11</v>
       </c>
+      <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
+      <c r="A28" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="B28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F28" t="b">
+      <c r="F28" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1417,6 +1483,7 @@
       <c r="E29" t="s">
         <v>43</v>
       </c>
+      <c r="F29"/>
     </row>
     <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
@@ -1434,6 +1501,7 @@
       <c r="E30" t="s">
         <v>11</v>
       </c>
+      <c r="F30"/>
     </row>
     <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
@@ -1451,6 +1519,7 @@
       <c r="E31" t="s">
         <v>11</v>
       </c>
+      <c r="F31"/>
     </row>
     <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
@@ -1468,6 +1537,7 @@
       <c r="E32" t="s">
         <v>11</v>
       </c>
+      <c r="F32"/>
     </row>
     <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
@@ -1485,6 +1555,7 @@
       <c r="E33" t="s">
         <v>11</v>
       </c>
+      <c r="F33"/>
     </row>
     <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
@@ -1502,6 +1573,7 @@
       <c r="E34" t="s">
         <v>11</v>
       </c>
+      <c r="F34"/>
     </row>
     <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
@@ -1519,6 +1591,7 @@
       <c r="E35" t="s">
         <v>11</v>
       </c>
+      <c r="F35"/>
     </row>
     <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
@@ -1536,6 +1609,7 @@
       <c r="E36" t="s">
         <v>11</v>
       </c>
+      <c r="F36"/>
     </row>
     <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
@@ -1553,6 +1627,7 @@
       <c r="E37" t="s">
         <v>11</v>
       </c>
+      <c r="F37"/>
     </row>
     <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
@@ -1570,6 +1645,7 @@
       <c r="E38" t="s">
         <v>11</v>
       </c>
+      <c r="F38"/>
     </row>
     <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
@@ -1587,6 +1663,7 @@
       <c r="E39" t="s">
         <v>11</v>
       </c>
+      <c r="F39"/>
     </row>
     <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
@@ -1604,6 +1681,7 @@
       <c r="E40" t="s">
         <v>11</v>
       </c>
+      <c r="F40"/>
     </row>
     <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
@@ -1621,6 +1699,7 @@
       <c r="E41" t="s">
         <v>9</v>
       </c>
+      <c r="F41"/>
     </row>
     <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
@@ -1638,6 +1717,7 @@
       <c r="E42" t="s">
         <v>57</v>
       </c>
+      <c r="F42"/>
     </row>
     <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
@@ -1655,6 +1735,7 @@
       <c r="E43" t="s">
         <v>11</v>
       </c>
+      <c r="F43"/>
     </row>
     <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
@@ -1672,6 +1753,7 @@
       <c r="E44" t="s">
         <v>60</v>
       </c>
+      <c r="F44"/>
     </row>
     <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
@@ -1689,6 +1771,7 @@
       <c r="E45" t="s">
         <v>62</v>
       </c>
+      <c r="F45"/>
     </row>
     <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
@@ -1706,24 +1789,25 @@
       <c r="E46" t="s">
         <v>25</v>
       </c>
+      <c r="F46"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
+      <c r="A47" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B47" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="B47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F47" t="b">
+      <c r="F47" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1743,6 +1827,7 @@
       <c r="E48" t="s">
         <v>11</v>
       </c>
+      <c r="F48"/>
     </row>
     <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
@@ -1760,6 +1845,7 @@
       <c r="E49" t="s">
         <v>11</v>
       </c>
+      <c r="F49"/>
     </row>
     <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
@@ -1777,6 +1863,7 @@
       <c r="E50" t="s">
         <v>68</v>
       </c>
+      <c r="F50"/>
     </row>
     <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
@@ -1794,6 +1881,7 @@
       <c r="E51" t="s">
         <v>70</v>
       </c>
+      <c r="F51"/>
     </row>
     <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
@@ -1811,6 +1899,7 @@
       <c r="E52" t="s">
         <v>72</v>
       </c>
+      <c r="F52"/>
     </row>
     <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
@@ -1828,6 +1917,7 @@
       <c r="E53" t="s">
         <v>9</v>
       </c>
+      <c r="F53"/>
     </row>
     <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
@@ -1845,6 +1935,7 @@
       <c r="E54" t="s">
         <v>11</v>
       </c>
+      <c r="F54"/>
     </row>
     <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
@@ -1862,6 +1953,7 @@
       <c r="E55" t="s">
         <v>76</v>
       </c>
+      <c r="F55"/>
     </row>
     <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
@@ -1879,61 +1971,63 @@
       <c r="E56" t="s">
         <v>78</v>
       </c>
+      <c r="F56"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
+      <c r="A57" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B57" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" t="b">
+      <c r="B57" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A58" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="C58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="F58" s="10"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
+      <c r="A59" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B59" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="B59" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F59" t="b">
+      <c r="F59" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1953,6 +2047,7 @@
       <c r="E60" t="s">
         <v>11</v>
       </c>
+      <c r="F60"/>
     </row>
     <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
@@ -1970,6 +2065,7 @@
       <c r="E61" t="s">
         <v>11</v>
       </c>
+      <c r="F61"/>
     </row>
     <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
@@ -1987,24 +2083,25 @@
       <c r="E62" t="s">
         <v>11</v>
       </c>
+      <c r="F62"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A63" t="s">
+      <c r="A63" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B63" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" t="s">
-        <v>8</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="B63" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F63" t="b">
+      <c r="F63" s="6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2024,6 +2121,7 @@
       <c r="E64" t="s">
         <v>11</v>
       </c>
+      <c r="F64"/>
     </row>
     <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
@@ -2041,6 +2139,7 @@
       <c r="E65" t="s">
         <v>11</v>
       </c>
+      <c r="F65"/>
     </row>
     <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
@@ -2058,6 +2157,7 @@
       <c r="E66" t="s">
         <v>11</v>
       </c>
+      <c r="F66"/>
     </row>
     <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
@@ -2075,6 +2175,7 @@
       <c r="E67" t="s">
         <v>11</v>
       </c>
+      <c r="F67"/>
     </row>
     <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
@@ -2092,43 +2193,45 @@
       <c r="E68" t="s">
         <v>11</v>
       </c>
+      <c r="F68"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A69" t="s">
+      <c r="A69" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B69" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69" t="s">
-        <v>8</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="B69" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F69" t="b">
+      <c r="F69" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70"/>
     </row>
     <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
@@ -2146,522 +2249,528 @@
       <c r="E71" t="s">
         <v>96</v>
       </c>
+      <c r="F71"/>
     </row>
     <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A73" t="s">
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72"/>
+    </row>
+    <row r="73" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A73" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B73" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" t="s">
-        <v>8</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="B73" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" s="6" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A74" t="s">
+    <row r="74" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A74" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B74" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" t="s">
-        <v>8</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="B74" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="6" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A75" s="2" t="s">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A75" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="2" t="s">
+      <c r="C75" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="10"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A76" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A77" s="2" t="s">
+      <c r="C76" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="10"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A77" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A78" s="2" t="s">
+      <c r="C77" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="10"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A78" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A79" s="2" t="s">
+      <c r="C78" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="10"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A79" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A80" s="2" t="s">
+      <c r="C79" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="10"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A80" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A81" s="2" t="s">
+      <c r="C80" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="10"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A81" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E81" s="2" t="s">
+      <c r="C81" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="8" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A82" s="2" t="s">
+      <c r="F81" s="10"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A82" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A83" s="2" t="s">
+      <c r="C82" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="10"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A83" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="2" t="s">
+      <c r="C83" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="8" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A84" s="2" t="s">
+      <c r="F83" s="10"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A84" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="C84" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="10"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C85" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" t="b">
+      <c r="C85" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" t="b">
+      <c r="C86" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A87" s="4" t="s">
+    <row r="87" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A87" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E87" s="4" t="s">
+      <c r="C87" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F87" s="11" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" s="4" t="s">
+      <c r="C88" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="4" t="s">
+      <c r="C89" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="F89" t="b">
+      <c r="F89" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F90" t="b">
+      <c r="C90" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C91" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F91" s="4" t="s">
+      <c r="C91" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" t="b">
+      <c r="C92" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F93" t="b">
+      <c r="C93" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F93" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C94" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" t="b">
+      <c r="C94" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C95" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F95" t="b">
+      <c r="C95" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F95" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C96" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F96" t="b">
+      <c r="C96" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E97" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F97" t="b">
+      <c r="C97" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A98" t="s">
+    <row r="98" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A98" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B98" t="s">
-        <v>6</v>
-      </c>
-      <c r="C98" t="s">
-        <v>8</v>
-      </c>
-      <c r="D98" t="s">
-        <v>8</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="B98" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" s="13" t="s">
         <v>155</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E98" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Both"/>
-        <filter val="Inst"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="3">
       <filters>
         <filter val="Y"/>
@@ -2682,10 +2791,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>130</v>
       </c>
     </row>
